--- a/output/第10期計画_将来推計_需要3シナリオの感度表.xlsx
+++ b/output/第10期計画_将来推計_需要3シナリオの感度表.xlsx
@@ -866,22 +866,22 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>+0.0％ 〜 +13.5％</t>
+          <t>+0.0％ 〜 +13.4％</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -898,22 +898,22 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>135</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>158</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>-9.9％ 〜 +5.4％</t>
+          <t>-9.8％ 〜 +5.4％</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -930,22 +930,22 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>302</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>349</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>368</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>-13.5％ 〜 +5.4％</t>
+          <t>-13.4％ 〜 +5.4％</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -962,22 +962,22 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>15112</t>
+          <t>15604</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>16136</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>21279</t>
+          <t>21948</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>-3.4％ 〜 +36.0％</t>
+          <t>-3.3％ 〜 +36.0％</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -1087,22 +1087,22 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>153</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>356</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -1119,22 +1119,22 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>349</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -1151,22 +1151,22 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>158</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>368</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -1222,17 +1222,17 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>+69</t>
+          <t>+71</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
@@ -1254,17 +1254,17 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>150</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>140</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1286,17 +1286,17 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>349</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>317</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>-32</t>
+          <t>-33</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -1362,12 +1362,12 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>16136</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>19351</t>
+          <t>19960</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
@@ -1394,12 +1394,12 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>786</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>956</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>710</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>464</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
@@ -1490,12 +1490,12 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -1522,12 +1522,12 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>218</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>218</t>
         </is>
       </c>
       <c r="E23" s="17" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -1586,12 +1586,12 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>587</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>719</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
@@ -1652,22 +1652,22 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>537</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>349</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>16136</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr"/>
@@ -1680,22 +1680,22 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>589</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>336</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>15112</t>
+          <t>15604</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -1808,27 +1808,27 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>+0 〜 +53</t>
+          <t>+0 〜 +54</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>+0.0％ 〜 +2.6％</t>
+          <t>+0.0％ 〜 +2.7％</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -1845,22 +1845,22 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>+0 〜 +80</t>
+          <t>+0 〜 +82</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>+0 〜 +108</t>
+          <t>+0 〜 +111</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -1963,22 +1963,22 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>+0 〜 +67</t>
+          <t>+0 〜 +68</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -1996,22 +1996,22 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>+0 〜 +102</t>
+          <t>+0 〜 +105</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -2029,27 +2029,27 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>+0 〜 +138</t>
+          <t>+0 〜 +142</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>+0.0％ 〜 +13.5％</t>
+          <t>+0.0％ 〜 +13.4％</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr"/>
@@ -2106,17 +2106,17 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>140</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>147</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>-4.7％ 〜 +2.6％</t>
+          <t>-4.6％ 〜 +2.7％</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr"/>
@@ -2139,22 +2139,22 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>138</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>148</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>154</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>-10 〜 +6</t>
+          <t>-11 〜 +6</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -2172,27 +2172,27 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>135</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>158</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>-14 〜 +8</t>
+          <t>-15 〜 +8</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>-9.9％ 〜 +5.4％</t>
+          <t>-9.8％ 〜 +5.4％</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr"/>
@@ -2249,17 +2249,17 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>319</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>342</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>351</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>-6.7％ 〜 +2.6％</t>
+          <t>-6.7％ 〜 +2.7％</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr"/>
@@ -2282,22 +2282,22 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>311</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>346</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>359</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>-34 〜 +14</t>
+          <t>-35 〜 +14</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -2315,27 +2315,27 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>302</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>349</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>368</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>-46 〜 +18</t>
+          <t>-47 〜 +19</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>-13.5％ 〜 +5.4％</t>
+          <t>-13.4％ 〜 +5.4％</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr"/>
@@ -2448,22 +2448,22 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>15112</t>
+          <t>15604</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>16136</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>21279</t>
+          <t>21948</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>-3.4％ 〜 +36.0％</t>
+          <t>-3.3％ 〜 +36.0％</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>-1.9％ 〜 +19.2％</t>
+          <t>-1.8％ 〜 +19.2％</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -2532,22 +2532,22 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>776</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>786</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>-1.3％ 〜 +28.2％</t>
+          <t>-1.2％ 〜 +28.2％</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
@@ -2574,22 +2574,22 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>464</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>710</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>766</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>-34.7％ 〜 +8.0％</t>
+          <t>-34.7％ 〜 +7.9％</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -2616,22 +2616,22 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>+0.0％ 〜 +16.7％</t>
+          <t>+0.0％ 〜 +16.6％</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -2658,22 +2658,22 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>139</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>218</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>-36.4％ 〜 +7.8％</t>
+          <t>-36.4％ 〜 +7.7％</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
@@ -2700,22 +2700,22 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>-43.5％ 〜 +5.4％</t>
+          <t>-43.4％ 〜 +5.4％</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
@@ -2742,17 +2742,17 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>587</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>587</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>782</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -2829,22 +2829,22 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>194</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>199</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>209</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>-2.3％ 〜 +5.4％</t>
+          <t>-2.2％ 〜 +5.4％</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr"/>
@@ -2867,17 +2867,17 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>672</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>672</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>710</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -2905,17 +2905,17 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
@@ -3062,47 +3062,47 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>15303</t>
+          <t>15540</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>15569</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>18306</t>
+          <t>18584</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>15210</t>
+          <t>15571</t>
         </is>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>15970</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>19775</t>
+          <t>20232</t>
         </is>
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>15112</t>
+          <t>15604</t>
         </is>
       </c>
       <c r="J5" s="13" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>16136</t>
         </is>
       </c>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>21279</t>
+          <t>21948</t>
         </is>
       </c>
     </row>
@@ -3119,47 +3119,47 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="J6" s="13" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1546</t>
         </is>
       </c>
     </row>
@@ -3176,47 +3176,47 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>575</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>695</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>723</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>520</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>744</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>464</t>
         </is>
       </c>
       <c r="J7" s="13" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>710</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>766</t>
         </is>
       </c>
     </row>
@@ -3233,47 +3233,47 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1647</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="J8" s="13" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1810</t>
         </is>
       </c>
     </row>
@@ -3290,47 +3290,47 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>174</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>213</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>234</t>
         </is>
       </c>
     </row>
@@ -3347,47 +3347,47 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>575</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>575</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>581</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>581</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>724</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>587</t>
         </is>
       </c>
       <c r="J10" s="13" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>587</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>782</t>
         </is>
       </c>
     </row>
@@ -3477,47 +3477,47 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="J14" s="13" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1201</t>
         </is>
       </c>
     </row>
@@ -3534,47 +3534,47 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
         <is>
           <t>135</t>
         </is>
       </c>
-      <c r="G15" s="13" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="J15" s="13" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>158</t>
         </is>
       </c>
     </row>
@@ -3591,47 +3591,47 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>319</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>342</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
           <t>346</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>359</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>302</t>
         </is>
       </c>
       <c r="J16" s="13" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>349</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>368</t>
         </is>
       </c>
     </row>
@@ -3729,17 +3729,17 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>302</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>349</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>368</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>77.2％</t>
+          <t>79.7％</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
@@ -3766,17 +3766,17 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>135</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>158</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>60.1％</t>
+          <t>62.0％</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -3847,17 +3847,17 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>351</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>359</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>368</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>77.2％</t>
+          <t>79.7％</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -3884,17 +3884,17 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>151</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>154</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>158</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>60.1％</t>
+          <t>62.0％</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">

--- a/output/第10期計画_将来推計_需要3シナリオの感度表.xlsx
+++ b/output/第10期計画_将来推計_需要3シナリオの感度表.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,9 +202,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
@@ -876,12 +873,12 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>+0.0％ 〜 +13.4％</t>
+          <t>+0.0％ 〜 +10.6％</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -898,7 +895,7 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>147</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -908,12 +905,12 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>159</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>-9.8％ 〜 +5.4％</t>
+          <t>-2.3％ 〜 +6.1％</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -930,7 +927,7 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>323</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -945,7 +942,7 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>-13.4％ 〜 +5.4％</t>
+          <t>-7.6％ 〜 +5.4％</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -1227,17 +1224,17 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>+71</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
-          <t>+6.7％</t>
+          <t>+42</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>+4.0％</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -1259,17 +1256,17 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>151</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>-10</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>-6.4％</t>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>+0.7％</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -1291,17 +1288,17 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>336</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>-33</t>
-        </is>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>-9.3％</t>
+          <t>-13</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>-3.7％</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -1367,15 +1364,15 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>19960</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>+23.7％</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
+          <t>17333</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>+7.4％</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>47→51→55（合計の趨勢で一様に延長すると+29.1％）</t>
         </is>
@@ -1399,15 +1396,15 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>1467</t>
-        </is>
-      </c>
-      <c r="E19" s="15" t="inlineStr">
-        <is>
-          <t>+13.1％</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
+          <t>1316</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>+1.5％</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>8→8→8（合計の趨勢で一様に延長すると+0.0％）</t>
         </is>
@@ -1431,15 +1428,15 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>956</t>
-        </is>
-      </c>
-      <c r="E20" s="15" t="inlineStr">
-        <is>
-          <t>+21.7％</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="inlineStr">
+          <t>826</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>+5.2％</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
         <is>
           <t>11→11→12（合計の趨勢で一様に延長すると+16.7％）</t>
         </is>
@@ -1463,15 +1460,15 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>-34.7％</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
+          <t>639</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>-10.0％</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
         <is>
           <t>10→9→9（合計の趨勢で一様に延長すると-22.2％）</t>
         </is>
@@ -1495,12 +1492,12 @@
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1613</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>+9.8％</t>
+          <t>+3.9％</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -1530,12 +1527,12 @@
           <t>218</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>+0.0％</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F23" s="15" t="inlineStr">
         <is>
           <t>13→10→11（合計の趨勢で一様に延長すると-36.4％）</t>
         </is>
@@ -1559,15 +1556,15 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>-40.0％</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>-10.0％</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>6→6→6（合計の趨勢で一様に延長すると+0.0％）</t>
         </is>
@@ -1591,15 +1588,15 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="E25" s="15" t="inlineStr">
-        <is>
-          <t>+22.6％</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
+          <t>623</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>+6.1％</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
         <is>
           <t>7→7→8（合計の趨勢で一様に延長すると+25.0％）</t>
         </is>
@@ -1673,7 +1670,7 @@
       <c r="F29" s="12" t="inlineStr"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>要介護1への集中が続く（年13人・4年で52人）</t>
         </is>
@@ -1707,7 +1704,7 @@
     <row r="32" ht="132" customHeight="1">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>注1）見込量を最も動かすのは③の1人当たり利用日数・回数である。訪問介護は直近3年の趨勢を延長すると2割以上動く。注2）②の利用率の趨勢は、在宅では上向き、居住系・施設では下向きであり、向きが揃っていない。低位・高位はサービスごとに異なるレバーの組合せから生じる。注3）灰色に網掛けした種別（短期入所生活介護・短期入所療養介護）は月平均の実数が300未満であり、要介護度別の趨勢の振れが増幅されやすい。注3-2）右端の列は、1人当たりの合計の推移と、その趨勢を全要介護度に一様に掛けた場合の差の割合である。要介護度別に延長した場合（左から2列目）との差が10ポイント以上ある種別（訪問看護・通所介護・短期入所生活介護・短期入所療養介護）は、2つの置き方が一致しない。要介護度別の趨勢は要介護度ごとの振れを増幅し、合計の趨勢は要介護度別の構成の変化を反映しない。これらの種別の低位・高位は置き方に依存するため、幅の広い方を上下限として読む（03シートは両方を候補に含めている）。注4）④の要介護1への集中は、要介護1の1人当たり利用回数が要介護5より大幅に少ないため、在宅の利用者数を増やす一方で訪問介護の見込量を減らす。</t>
+          <t>注1）見込量を最も動かすのは③の1人当たり利用日数・回数である。訪問介護は直近3年の趨勢を延長すると2割以上動く。注2）②の利用率の趨勢は、在宅では上向き、居住系・施設では下向きであり、向きが揃っていない。低位・高位はサービスごとに異なるレバーの組合せから生じる。注3）灰色に網掛けした種別（短期入所生活介護・短期入所療養介護）は月平均の実数が300未満であり、要介護度別の趨勢の振れが増幅されやすい。注3-2）右端の列は、1人当たりの合計の推移と、その趨勢を全要介護度に一様に掛けた場合の差の割合である。要介護度別に延長した場合（左から2列目）との差が10ポイント以上ある種別（訪問介護・訪問リハビリテーション・通所介護・短期入所生活介護・地域密着型通所介護）は、2つの置き方が一致しない。要介護度別の趨勢は要介護度ごとの振れを増幅し、合計の趨勢は要介護度別の構成の変化を反映しない。これらの種別の低位・高位は置き方に依存するため、幅の広い方を上下限として読む（03シートは両方を候補に含めている）。注4）④の要介護1への集中は、要介護1の1人当たり利用回数が要介護5より大幅に少ないため、在宅の利用者数を増やす一方で訪問介護の見込量を減らす。</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1970,17 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>+0 〜 +68</t>
+          <t>+0 〜 +64</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>+0.0％ 〜 +6.6％</t>
+          <t>+0.0％ 〜 +6.1％</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr"/>
@@ -2006,17 +2003,17 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>+0 〜 +105</t>
+          <t>+0 〜 +89</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>+0.0％ 〜 +10.0％</t>
+          <t>+0.0％ 〜 +8.5％</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr"/>
@@ -2039,17 +2036,17 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>+0 〜 +142</t>
+          <t>+0 〜 +112</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>+0.0％ 〜 +13.4％</t>
+          <t>+0.0％ 〜 +10.6％</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr"/>
@@ -2106,7 +2103,7 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>145</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -2116,17 +2113,17 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>152</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>-7 〜 +4</t>
+          <t>-2 〜 +5</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>-4.6％ 〜 +2.7％</t>
+          <t>-1.2％ 〜 +3.4％</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr"/>
@@ -2139,7 +2136,7 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>146</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -2149,17 +2146,17 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>156</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>-11 〜 +6</t>
+          <t>-3 〜 +7</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>-7.2％ 〜 +4.0％</t>
+          <t>-1.7％ 〜 +4.8％</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr"/>
@@ -2172,7 +2169,7 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>147</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -2182,17 +2179,17 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>159</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>-15 〜 +8</t>
+          <t>-3 〜 +9</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>-9.8％ 〜 +5.4％</t>
+          <t>-2.3％ 〜 +6.1％</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr"/>
@@ -2249,7 +2246,7 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>324</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -2264,12 +2261,12 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>-23 〜 +9</t>
+          <t>-19 〜 +9</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>-6.7％ 〜 +2.7％</t>
+          <t>-5.4％ 〜 +2.7％</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr"/>
@@ -2282,7 +2279,7 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>324</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
@@ -2297,12 +2294,12 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>-35 〜 +14</t>
+          <t>-22 〜 +14</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>-10.1％ 〜 +4.0％</t>
+          <t>-6.4％ 〜 +4.0％</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr"/>
@@ -2315,7 +2312,7 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>323</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -2330,12 +2327,12 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>-47 〜 +19</t>
+          <t>-27 〜 +19</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>-13.4％ 〜 +5.4％</t>
+          <t>-7.6％ 〜 +5.4％</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr"/>
@@ -2500,12 +2497,12 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>-1.8％ 〜 +19.2％</t>
+          <t>-1.8％ 〜 +7.0％</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -2515,7 +2512,7 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>1人当たりの日数・回数</t>
+          <t>認定者数</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2539,12 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>966</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>-1.2％ 〜 +28.2％</t>
+          <t>-1.2％ 〜 +22.9％</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
@@ -2557,7 +2554,7 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>1人当たりの日数・回数</t>
+          <t>認定者数</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2571,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>552</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -2589,7 +2586,7 @@
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>-34.7％ 〜 +7.9％</t>
+          <t>-22.2％ 〜 +7.9％</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -2626,12 +2623,12 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>+0.0％ 〜 +16.6％</t>
+          <t>+0.0％ 〜 +10.8％</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -2641,7 +2638,7 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>1人当たりの日数・回数</t>
+          <t>認定者数</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2673,7 @@
           <t>-36.4％ 〜 +7.7％</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>小（300未満）</t>
         </is>
@@ -2700,7 +2697,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
@@ -2715,10 +2712,10 @@
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>-43.4％ 〜 +5.4％</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
+          <t>-15.1％ 〜 +5.4％</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>小（300未満）</t>
         </is>
@@ -3129,7 +3126,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -3144,7 +3141,7 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
@@ -3159,7 +3156,7 @@
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1387</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3173,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>618</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
@@ -3191,7 +3188,7 @@
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>585</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
@@ -3206,7 +3203,7 @@
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>552</t>
         </is>
       </c>
       <c r="J7" s="13" t="inlineStr">
@@ -3243,7 +3240,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -3258,7 +3255,7 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="I8" s="12" t="inlineStr">
@@ -3273,7 +3270,7 @@
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1720</t>
         </is>
       </c>
     </row>
@@ -3487,7 +3484,7 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -3502,7 +3499,7 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
@@ -3517,7 +3514,7 @@
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1171</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3531,7 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>145</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
@@ -3544,12 +3541,12 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>146</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
@@ -3559,12 +3556,12 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>147</t>
         </is>
       </c>
       <c r="J15" s="13" t="inlineStr">
@@ -3574,7 +3571,7 @@
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>159</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3588,7 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>324</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
@@ -3606,7 +3603,7 @@
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>324</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
@@ -3621,7 +3618,7 @@
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>323</t>
         </is>
       </c>
       <c r="J16" s="13" t="inlineStr">
@@ -3729,7 +3726,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>323</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -3766,7 +3763,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>147</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -3776,7 +3773,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>159</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -3786,7 +3783,7 @@
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>62.0％</t>
+          <t>62.4％</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -3884,17 +3881,17 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>152</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>156</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>159</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -3904,7 +3901,7 @@
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>62.0％</t>
+          <t>62.4％</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -4002,7 +3999,7 @@
           <t>より適切と思われるサービス（小規模多機能型居宅介護）</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>44件</t>
         </is>
@@ -4032,7 +4029,7 @@
           <t>24時間対応の3サービスを必要とする回答</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>延べ26件</t>
         </is>
@@ -4062,7 +4059,7 @@
           <t>特別養護老人ホームの待機者</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>82〜137人</t>
         </is>
@@ -4092,7 +4089,7 @@
           <t>在宅生活の維持が困難とされた方</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>72人</t>
         </is>
@@ -4122,7 +4119,7 @@
           <t>認定を受けているがサービスを利用していない方</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>486人</t>
         </is>
